--- a/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 11,88</t>
+          <t>-8,97; 12,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 7,67</t>
+          <t>-12,78; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,54; 68,08</t>
+          <t>46,19; 66,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 14,46</t>
+          <t>-7,81; 13,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 11,0</t>
+          <t>-11,11; 10,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,39; 59,81</t>
+          <t>37,19; 60,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 10,03</t>
+          <t>-5,41; 9,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 6,11</t>
+          <t>-9,27; 5,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,85; 61,09</t>
+          <t>45,19; 60,58</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 49,05</t>
+          <t>-25,61; 55,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 35,66</t>
+          <t>-36,72; 42,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129,28; 309,58</t>
+          <t>128,09; 298,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 55,8</t>
+          <t>-21,15; 55,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,94; 45,23</t>
+          <t>-29,99; 41,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,79; 243,67</t>
+          <t>99,58; 251,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 38,82</t>
+          <t>-15,52; 37,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 22,51</t>
+          <t>-27,01; 22,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>130,74; 243,32</t>
+          <t>128,77; 236,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 12,2</t>
+          <t>-4,45; 12,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 6,35</t>
+          <t>-8,81; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,98; 53,28</t>
+          <t>38,29; 53,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 3,26</t>
+          <t>-13,71; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 2,42</t>
+          <t>-11,71; 2,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,09; 49,57</t>
+          <t>34,25; 49,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,66</t>
+          <t>-6,94; 5,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 2,59</t>
+          <t>-8,09; 3,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,46; 49,92</t>
+          <t>38,6; 49,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 45,42</t>
+          <t>-13,0; 46,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 23,64</t>
+          <t>-25,79; 26,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103,45; 201,44</t>
+          <t>110,99; 204,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 10,41</t>
+          <t>-34,66; 6,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 7,42</t>
+          <t>-30,9; 8,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,99; 165,52</t>
+          <t>86,15; 162,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 15,98</t>
+          <t>-19,68; 17,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 8,73</t>
+          <t>-22,79; 11,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>106,93; 173,0</t>
+          <t>106,81; 169,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 14,93</t>
+          <t>-10,4; 14,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 6,3</t>
+          <t>-14,2; 6,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,31; 52,44</t>
+          <t>32,37; 51,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 9,08</t>
+          <t>-13,61; 8,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 6,8</t>
+          <t>-13,88; 6,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,44; 44,42</t>
+          <t>25,28; 44,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 7,57</t>
+          <t>-8,03; 8,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 3,56</t>
+          <t>-11,77; 3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,6; 44,58</t>
+          <t>31,02; 45,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 47,75</t>
+          <t>-24,35; 45,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 21,41</t>
+          <t>-32,72; 22,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,19; 176,2</t>
+          <t>73,47; 172,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 26,18</t>
+          <t>-29,32; 24,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,72; 19,92</t>
+          <t>-29,88; 19,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,76; 132,65</t>
+          <t>53,59; 133,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 21,54</t>
+          <t>-18,41; 24,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,88; 10,25</t>
+          <t>-26,83; 10,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69,38; 130,7</t>
+          <t>70,41; 138,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 10,55</t>
+          <t>-8,2; 11,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 20,85</t>
+          <t>2,1; 21,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,78; 49,68</t>
+          <t>31,63; 50,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 8,59</t>
+          <t>-10,83; 8,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 4,12</t>
+          <t>-15,56; 3,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,93; 41,43</t>
+          <t>20,56; 40,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 6,61</t>
+          <t>-6,01; 7,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 10,08</t>
+          <t>-3,79; 9,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,75; 42,66</t>
+          <t>29,14; 42,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 33,61</t>
+          <t>-20,24; 36,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 67,95</t>
+          <t>5,33; 68,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,0; 162,43</t>
+          <t>78,11; 169,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 22,34</t>
+          <t>-24,09; 21,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 10,55</t>
+          <t>-34,15; 10,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,66; 114,06</t>
+          <t>46,29; 115,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 18,28</t>
+          <t>-14,9; 23,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 28,48</t>
+          <t>-9,19; 27,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,08; 125,17</t>
+          <t>70,63; 126,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,52</t>
+          <t>-2,38; 7,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,68</t>
+          <t>-3,69; 5,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,83; 49,82</t>
+          <t>40,01; 50,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,18</t>
+          <t>-7,06; 2,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,42</t>
+          <t>-9,02; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,38; 42,66</t>
+          <t>33,1; 42,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,49</t>
+          <t>-3,6; 3,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,03</t>
+          <t>-5,18; 1,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,31; 44,87</t>
+          <t>37,91; 44,76</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 24,59</t>
+          <t>-7,02; 24,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 18,32</t>
+          <t>-10,68; 19,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110,54; 165,8</t>
+          <t>110,29; 166,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 9,37</t>
+          <t>-17,82; 6,14</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 1,23</t>
+          <t>-22,12; 1,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,5; 122,86</t>
+          <t>83,62; 123,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 10,57</t>
+          <t>-9,66; 10,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 6,1</t>
+          <t>-14,18; 4,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>103,81; 134,42</t>
+          <t>101,06; 134,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 12,08</t>
+          <t>-11,31; 11,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 8,81</t>
+          <t>-13,79; 7,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,19; 66,5</t>
+          <t>45,39; 66,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 13,86</t>
+          <t>-7,52; 14,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 10,39</t>
+          <t>-10,66; 11,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,19; 60,54</t>
+          <t>37,64; 60,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 9,93</t>
+          <t>-4,74; 10,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 5,92</t>
+          <t>-9,4; 5,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,19; 60,58</t>
+          <t>45,18; 60,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 55,62</t>
+          <t>-31,45; 48,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 42,41</t>
+          <t>-38,69; 34,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128,09; 298,74</t>
+          <t>117,44; 299,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 55,76</t>
+          <t>-20,63; 58,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 41,14</t>
+          <t>-29,15; 43,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,58; 251,47</t>
+          <t>101,28; 248,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 37,72</t>
+          <t>-13,85; 40,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 22,25</t>
+          <t>-26,76; 22,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>128,77; 236,47</t>
+          <t>129,66; 238,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 12,18</t>
+          <t>-3,54; 11,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 6,95</t>
+          <t>-8,64; 7,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,29; 53,31</t>
+          <t>38,29; 53,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 1,9</t>
+          <t>-13,46; 1,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 2,76</t>
+          <t>-11,96; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,25; 49,96</t>
+          <t>34,7; 50,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,04</t>
+          <t>-6,64; 4,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 3,3</t>
+          <t>-7,59; 2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,6; 49,53</t>
+          <t>39,1; 50,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 46,15</t>
+          <t>-10,5; 45,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 26,32</t>
+          <t>-25,19; 28,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110,99; 204,49</t>
+          <t>107,58; 206,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 6,87</t>
+          <t>-35,28; 5,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 8,28</t>
+          <t>-30,57; 10,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,15; 162,94</t>
+          <t>90,56; 168,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 17,11</t>
+          <t>-19,31; 14,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 11,03</t>
+          <t>-21,94; 8,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>106,81; 169,15</t>
+          <t>108,63; 169,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 14,26</t>
+          <t>-7,98; 16,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 6,68</t>
+          <t>-13,89; 7,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,37; 51,14</t>
+          <t>32,1; 52,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 8,43</t>
+          <t>-12,27; 10,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 6,76</t>
+          <t>-13,39; 6,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,28; 44,87</t>
+          <t>25,24; 43,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 8,83</t>
+          <t>-8,17; 8,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 3,5</t>
+          <t>-11,73; 2,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,02; 45,95</t>
+          <t>31,68; 44,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 45,04</t>
+          <t>-18,61; 55,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 22,17</t>
+          <t>-32,39; 26,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73,47; 172,8</t>
+          <t>70,86; 181,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 24,13</t>
+          <t>-27,25; 29,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 19,11</t>
+          <t>-29,06; 19,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,59; 133,91</t>
+          <t>53,47; 126,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 24,92</t>
+          <t>-18,3; 24,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 10,33</t>
+          <t>-27,09; 7,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,41; 138,27</t>
+          <t>71,13; 132,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 11,27</t>
+          <t>-9,11; 11,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 21,32</t>
+          <t>1,91; 21,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,63; 50,38</t>
+          <t>31,3; 49,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 8,14</t>
+          <t>-10,7; 9,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 3,68</t>
+          <t>-15,31; 3,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,56; 40,95</t>
+          <t>20,7; 41,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 7,89</t>
+          <t>-6,42; 7,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 9,84</t>
+          <t>-3,6; 9,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,14; 42,88</t>
+          <t>28,58; 42,6</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 36,88</t>
+          <t>-22,45; 36,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 68,95</t>
+          <t>4,27; 71,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78,11; 169,39</t>
+          <t>77,17; 164,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 21,88</t>
+          <t>-23,2; 24,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 10,36</t>
+          <t>-33,2; 10,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,29; 115,04</t>
+          <t>44,95; 115,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 23,01</t>
+          <t>-15,74; 20,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 27,77</t>
+          <t>-8,69; 26,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,63; 126,4</t>
+          <t>67,87; 122,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,34</t>
+          <t>-1,92; 7,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,89</t>
+          <t>-3,58; 6,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,01; 50,01</t>
+          <t>39,69; 49,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 2,23</t>
+          <t>-6,68; 2,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 0,32</t>
+          <t>-8,87; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,76</t>
+          <t>33,02; 42,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,72</t>
+          <t>-3,03; 3,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 1,55</t>
+          <t>-4,56; 1,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,76</t>
+          <t>37,94; 44,93</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 24,17</t>
+          <t>-5,61; 25,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 19,58</t>
+          <t>-10,0; 19,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110,29; 166,04</t>
+          <t>109,53; 163,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 6,14</t>
+          <t>-17,07; 8,48</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 1,17</t>
+          <t>-22,54; 1,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,62; 123,77</t>
+          <t>83,66; 124,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 10,98</t>
+          <t>-8,28; 10,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 4,52</t>
+          <t>-12,24; 5,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>101,06; 134,81</t>
+          <t>102,94; 136,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50,52</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,53</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,52</t>
+          <t>57,45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53,39</t>
+          <t>53,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 11,6</t>
+          <t>-7,11; 14,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 7,79</t>
+          <t>-10,93; 11,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,39; 66,61</t>
+          <t>38,31; 60,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 14,32</t>
+          <t>-11,03; 11,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 11,4</t>
+          <t>-12,86; 7,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,64; 60,42</t>
+          <t>47,29; 67,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 10,49</t>
+          <t>-5,04; 10,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 5,91</t>
+          <t>-9,22; 6,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,18; 60,82</t>
+          <t>46,37; 61,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>161,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-8,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>197,08%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>157,92%</t>
+          <t>196,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175,91%</t>
+          <t>177,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 48,31</t>
+          <t>-19,62; 55,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 34,64</t>
+          <t>-29,94; 45,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117,44; 299,77</t>
+          <t>100,85; 247,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 58,49</t>
+          <t>-32,19; 49,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 43,81</t>
+          <t>-37,24; 35,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>101,28; 248,55</t>
+          <t>128,45; 308,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 40,36</t>
+          <t>-14,85; 38,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 22,2</t>
+          <t>-26,12; 22,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>129,66; 238,82</t>
+          <t>132,45; 243,23</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,85</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43,9</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,67</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46,01</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,85</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,62</t>
+          <t>45,07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44,34</t>
+          <t>44,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 11,93</t>
+          <t>-13,3; 3,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 7,48</t>
+          <t>-12,04; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,29; 53,43</t>
+          <t>36,72; 50,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 1,9</t>
+          <t>-5,92; 12,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 3,17</t>
+          <t>-10,0; 6,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,7; 50,25</t>
+          <t>36,81; 52,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 4,57</t>
+          <t>-6,46; 4,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 2,56</t>
+          <t>-8,48; 2,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,1; 50,05</t>
+          <t>38,63; 50,32</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-15,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-13,87%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>125,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-2,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>150,24%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-13,87%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>121,85%</t>
+          <t>147,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135,14%</t>
+          <t>135,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 45,66</t>
+          <t>-34,54; 10,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 28,37</t>
+          <t>-31,48; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107,58; 206,78</t>
+          <t>91,89; 168,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 5,89</t>
+          <t>-16,02; 45,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 10,59</t>
+          <t>-28,62; 23,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,56; 168,76</t>
+          <t>101,0; 197,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 14,79</t>
+          <t>-18,23; 15,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 8,56</t>
+          <t>-22,99; 8,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108,63; 169,3</t>
+          <t>106,96; 173,44</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,58</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,03</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,08</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>42,54</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,83</t>
+          <t>42,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38,32</t>
+          <t>38,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 16,61</t>
+          <t>-13,22; 9,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 7,44</t>
+          <t>-13,88; 6,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,1; 52,1</t>
+          <t>24,56; 44,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 10,44</t>
+          <t>-9,85; 14,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 6,79</t>
+          <t>-14,57; 6,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,24; 43,5</t>
+          <t>31,5; 52,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 8,35</t>
+          <t>-8,34; 7,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 2,47</t>
+          <t>-11,24; 3,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,68; 44,94</t>
+          <t>30,84; 44,68</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-3,79%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-8,77%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>85,62%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-11,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>114,75%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-3,79%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-8,77%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>115,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 55,91</t>
+          <t>-29,55; 26,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 26,22</t>
+          <t>-30,72; 19,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,86; 181,5</t>
+          <t>51,99; 132,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 29,7</t>
+          <t>-23,81; 47,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 19,43</t>
+          <t>-33,66; 21,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,47; 126,53</t>
+          <t>68,29; 177,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 24,27</t>
+          <t>-18,89; 21,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 7,01</t>
+          <t>-25,88; 10,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71,13; 132,14</t>
+          <t>69,85; 130,93</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-5,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34,41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,67</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>40,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-5,58</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,05</t>
+          <t>39,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36,18</t>
+          <t>37,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 11,47</t>
+          <t>-10,42; 8,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 21,75</t>
+          <t>-15,14; 4,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,3; 49,36</t>
+          <t>24,25; 43,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 9,03</t>
+          <t>-8,7; 10,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 3,3</t>
+          <t>1,2; 20,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,7; 41,28</t>
+          <t>32,04; 47,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 7,05</t>
+          <t>-6,91; 6,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,69</t>
+          <t>-3,92; 10,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,58; 42,6</t>
+          <t>31,18; 42,73</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-2,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-13,47%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>33,08%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>114,42%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-2,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-13,47%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>112,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 36,65</t>
+          <t>-23,21; 22,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,27; 71,46</t>
+          <t>-32,73; 10,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77,17; 164,14</t>
+          <t>52,97; 120,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 24,14</t>
+          <t>-20,98; 33,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 10,02</t>
+          <t>3,15; 67,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,95; 115,06</t>
+          <t>76,93; 155,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 20,3</t>
+          <t>-16,26; 18,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 26,8</t>
+          <t>-9,86; 28,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67,87; 122,03</t>
+          <t>75,25; 127,01</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>39,6</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>44,97</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,98</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,34</t>
+          <t>44,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41,52</t>
+          <t>42,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,84</t>
+          <t>-6,71; 3,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,17</t>
+          <t>-8,87; 0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,69; 49,51</t>
+          <t>34,21; 43,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,96</t>
+          <t>-2,33; 7,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,61</t>
+          <t>-3,79; 5,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,02; 42,94</t>
+          <t>39,69; 49,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,71</t>
+          <t>-3,2; 3,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,92</t>
+          <t>-4,87; 2,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>37,94; 44,93</t>
+          <t>39,0; 45,16</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-5,83%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-10,66%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>106,14%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>7,72%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>136,65%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-5,83%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-10,66%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>102,76%</t>
+          <t>135,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118,09%</t>
+          <t>119,51%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 25,77</t>
+          <t>-16,67; 9,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 19,76</t>
+          <t>-22,15; 1,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109,53; 163,0</t>
+          <t>84,68; 126,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 8,48</t>
+          <t>-6,75; 24,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 1,39</t>
+          <t>-10,76; 18,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,66; 124,13</t>
+          <t>110,17; 164,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 10,99</t>
+          <t>-8,62; 10,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 5,8</t>
+          <t>-13,37; 6,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>102,94; 136,72</t>
+          <t>104,99; 135,28</t>
         </is>
       </c>
     </row>
